--- a/artfynd/A 21117-2021 artfynd.xlsx
+++ b/artfynd/A 21117-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21117-2021 artfynd.xlsx
+++ b/artfynd/A 21117-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,128 +1151,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>113740884</v>
-      </c>
-      <c r="B6" t="n">
-        <v>104698</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>340</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Rinkaby skjutfält. Oredslund, 2,2 km SSO, Sk</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>456498</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6201453</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Åhus</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>M-Kri-0656</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-12-25</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-12-25</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21117-2021 artfynd.xlsx
+++ b/artfynd/A 21117-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,6 +1151,135 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125166237</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57586</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100094</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sommargylling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Oriolus oriolus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Horna - vid skjutfältet, Rinkaby skjutfält, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456432</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6201520</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åhus</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hörs fint i NO från skjutfältsgränsen (vid nål).  infart via Tvåans väg i norr.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21117-2021 artfynd.xlsx
+++ b/artfynd/A 21117-2021 artfynd.xlsx
@@ -1156,7 +1156,7 @@
         <v>125166237</v>
       </c>
       <c r="B6" t="n">
-        <v>57586</v>
+        <v>57700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 21117-2021 artfynd.xlsx
+++ b/artfynd/A 21117-2021 artfynd.xlsx
@@ -1156,12 +1156,7 @@
         <v>125166237</v>
       </c>
       <c r="B6" t="n">
-        <v>57700</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
